--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/44.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/44.xlsx
@@ -426,13 +426,13 @@
         <v>-18.53326178606168</v>
       </c>
       <c r="E2">
-        <v>-11.35344341624013</v>
+        <v>-12.87394196295156</v>
       </c>
       <c r="F2">
-        <v>1.464175858295284</v>
+        <v>0.6579634390402703</v>
       </c>
       <c r="G2">
-        <v>-14.71161529299615</v>
+        <v>-15.75979360054911</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.97702889424138</v>
       </c>
       <c r="E3">
-        <v>-12.33831405732431</v>
+        <v>-13.01594585088409</v>
       </c>
       <c r="F3">
-        <v>1.603375689732834</v>
+        <v>0.3729470528504638</v>
       </c>
       <c r="G3">
-        <v>-14.62095600340321</v>
+        <v>-16.91109209110484</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.37903044883334</v>
       </c>
       <c r="E4">
-        <v>-11.91957512278305</v>
+        <v>-13.2897736171799</v>
       </c>
       <c r="F4">
-        <v>1.174704507365346</v>
+        <v>0.8623771126637861</v>
       </c>
       <c r="G4">
-        <v>-12.99183323298232</v>
+        <v>-13.92805716676098</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.78905216865073</v>
       </c>
       <c r="E5">
-        <v>-12.94319591595086</v>
+        <v>-13.68835178543901</v>
       </c>
       <c r="F5">
-        <v>1.04928608480395</v>
+        <v>0.559382496921911</v>
       </c>
       <c r="G5">
-        <v>-13.05885191687932</v>
+        <v>-15.0631869529029</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.21616254495562</v>
       </c>
       <c r="E6">
-        <v>-13.07853841861811</v>
+        <v>-14.44869615674889</v>
       </c>
       <c r="F6">
-        <v>1.385076082642745</v>
+        <v>1.023823261095514</v>
       </c>
       <c r="G6">
-        <v>-12.96109150710464</v>
+        <v>-13.86070246249174</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.68017091742843</v>
       </c>
       <c r="E7">
-        <v>-13.58144809953994</v>
+        <v>-14.93044880710689</v>
       </c>
       <c r="F7">
-        <v>1.472509318822326</v>
+        <v>1.056366833951879</v>
       </c>
       <c r="G7">
-        <v>-11.42340600447842</v>
+        <v>-13.88866664066196</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.16748088231711</v>
       </c>
       <c r="E8">
-        <v>-13.95753333740296</v>
+        <v>-15.91489830010835</v>
       </c>
       <c r="F8">
-        <v>1.576614227173738</v>
+        <v>0.9725460309654158</v>
       </c>
       <c r="G8">
-        <v>-11.5036569388959</v>
+        <v>-12.68122460830574</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.67241562930906</v>
       </c>
       <c r="E9">
-        <v>-14.42442806454178</v>
+        <v>-16.61298973923478</v>
       </c>
       <c r="F9">
-        <v>1.626241235739948</v>
+        <v>0.6003577200720759</v>
       </c>
       <c r="G9">
-        <v>-10.23813800614424</v>
+        <v>-12.52578787414588</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.19574353837562</v>
       </c>
       <c r="E10">
-        <v>-15.09535771657021</v>
+        <v>-17.87066018301503</v>
       </c>
       <c r="F10">
-        <v>1.768999654369491</v>
+        <v>1.021967157762619</v>
       </c>
       <c r="G10">
-        <v>-10.86779052553146</v>
+        <v>-11.32039506947846</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.72872532810448</v>
       </c>
       <c r="E11">
-        <v>-15.47485742383501</v>
+        <v>-17.05959237434524</v>
       </c>
       <c r="F11">
-        <v>2.040133274504556</v>
+        <v>1.378487866034517</v>
       </c>
       <c r="G11">
-        <v>-10.78353383101147</v>
+        <v>-12.19109172012556</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.25428277159952</v>
       </c>
       <c r="E12">
-        <v>-15.93915280689343</v>
+        <v>-17.26204686180616</v>
       </c>
       <c r="F12">
-        <v>1.497078932394453</v>
+        <v>1.418099518391488</v>
       </c>
       <c r="G12">
-        <v>-9.731694060092073</v>
+        <v>-11.1265262121532</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.75886166522331</v>
       </c>
       <c r="E13">
-        <v>-16.39456785242282</v>
+        <v>-20.52558675338797</v>
       </c>
       <c r="F13">
-        <v>2.341704138628451</v>
+        <v>1.372495122850494</v>
       </c>
       <c r="G13">
-        <v>-9.184930979917121</v>
+        <v>-10.73036978019631</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.25102804517666</v>
       </c>
       <c r="E14">
-        <v>-18.42721869550574</v>
+        <v>-20.69373805024078</v>
       </c>
       <c r="F14">
-        <v>2.247517980425436</v>
+        <v>1.648170811551039</v>
       </c>
       <c r="G14">
-        <v>-8.920544192059847</v>
+        <v>-11.07064089290476</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.72204496726821</v>
       </c>
       <c r="E15">
-        <v>-18.35642958981783</v>
+        <v>-20.81724765032598</v>
       </c>
       <c r="F15">
-        <v>2.431105921260923</v>
+        <v>1.774764343901691</v>
       </c>
       <c r="G15">
-        <v>-9.313936318491441</v>
+        <v>-10.23427128895437</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.16399642409758</v>
       </c>
       <c r="E16">
-        <v>-20.86116479125237</v>
+        <v>-21.63425228841983</v>
       </c>
       <c r="F16">
-        <v>2.859149956085897</v>
+        <v>2.308292694930425</v>
       </c>
       <c r="G16">
-        <v>-7.646672752912608</v>
+        <v>-9.298896510106532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.57796766738791</v>
       </c>
       <c r="E17">
-        <v>-19.96529224984094</v>
+        <v>-23.33300515749519</v>
       </c>
       <c r="F17">
-        <v>3.015653358355538</v>
+        <v>1.958342782501685</v>
       </c>
       <c r="G17">
-        <v>-8.660944453052357</v>
+        <v>-9.844788916804655</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.976638569552701</v>
       </c>
       <c r="E18">
-        <v>-22.72026186799132</v>
+        <v>-23.51250481021123</v>
       </c>
       <c r="F18">
-        <v>3.451836057879955</v>
+        <v>2.681310867723455</v>
       </c>
       <c r="G18">
-        <v>-8.250536122548908</v>
+        <v>-9.295331052560737</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.362184721024905</v>
       </c>
       <c r="E19">
-        <v>-22.33217164553397</v>
+        <v>-23.90386459090211</v>
       </c>
       <c r="F19">
-        <v>3.432772989775811</v>
+        <v>2.702599042638792</v>
       </c>
       <c r="G19">
-        <v>-7.654022164009789</v>
+        <v>-9.178885923762413</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.740085026836597</v>
       </c>
       <c r="E20">
-        <v>-23.99645829893695</v>
+        <v>-25.34472539371465</v>
       </c>
       <c r="F20">
-        <v>3.587201737296227</v>
+        <v>3.311847540896516</v>
       </c>
       <c r="G20">
-        <v>-7.663612814437058</v>
+        <v>-9.014944398112164</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.126953257003965</v>
       </c>
       <c r="E21">
-        <v>-24.1184010470155</v>
+        <v>-26.2914979829723</v>
       </c>
       <c r="F21">
-        <v>3.897726874666016</v>
+        <v>3.337813983086062</v>
       </c>
       <c r="G21">
-        <v>-7.682529271648454</v>
+        <v>-7.919935113360669</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.538789143021768</v>
       </c>
       <c r="E22">
-        <v>-25.10116594768611</v>
+        <v>-24.88430185593278</v>
       </c>
       <c r="F22">
-        <v>3.994084293679099</v>
+        <v>2.636704206909187</v>
       </c>
       <c r="G22">
-        <v>-6.626647324625605</v>
+        <v>-7.039932519202681</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.982322289803069</v>
       </c>
       <c r="E23">
-        <v>-23.85964857069122</v>
+        <v>-26.20397616582606</v>
       </c>
       <c r="F23">
-        <v>4.27693892129433</v>
+        <v>3.344554235462172</v>
       </c>
       <c r="G23">
-        <v>-7.328211514216877</v>
+        <v>-7.667499394900163</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.465782800493378</v>
       </c>
       <c r="E24">
-        <v>-25.47899011956807</v>
+        <v>-26.01200056721889</v>
       </c>
       <c r="F24">
-        <v>4.612035255942163</v>
+        <v>3.285052820513196</v>
       </c>
       <c r="G24">
-        <v>-7.138447733360313</v>
+        <v>-7.312284479627443</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.008106553238506</v>
       </c>
       <c r="E25">
-        <v>-25.02009720600079</v>
+        <v>-27.85420190743522</v>
       </c>
       <c r="F25">
-        <v>4.495208437972026</v>
+        <v>3.390139626532181</v>
       </c>
       <c r="G25">
-        <v>-5.805466503609387</v>
+        <v>-6.490597145143717</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.617997411244667</v>
       </c>
       <c r="E26">
-        <v>-26.55925759409783</v>
+        <v>-29.03617437970325</v>
       </c>
       <c r="F26">
-        <v>4.495784906925246</v>
+        <v>3.156435312002612</v>
       </c>
       <c r="G26">
-        <v>-6.884221009763061</v>
+        <v>-7.227577550914111</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.296908972329461</v>
       </c>
       <c r="E27">
-        <v>-25.55996829177323</v>
+        <v>-26.17782422843176</v>
       </c>
       <c r="F27">
-        <v>4.631879091062619</v>
+        <v>3.171444092963232</v>
       </c>
       <c r="G27">
-        <v>-6.212895343127492</v>
+        <v>-6.343284489737227</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.044834493673053</v>
       </c>
       <c r="E28">
-        <v>-25.78903662097723</v>
+        <v>-27.39659960896013</v>
       </c>
       <c r="F28">
-        <v>4.559687440613227</v>
+        <v>3.642409725508446</v>
       </c>
       <c r="G28">
-        <v>-6.325394301643006</v>
+        <v>-6.938060411868228</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.869664338798049</v>
       </c>
       <c r="E29">
-        <v>-25.75867773122981</v>
+        <v>-27.50244363194141</v>
       </c>
       <c r="F29">
-        <v>4.325127924889322</v>
+        <v>3.131868865842315</v>
       </c>
       <c r="G29">
-        <v>-6.436804090676099</v>
+        <v>-5.668115279730565</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.76443488895241</v>
       </c>
       <c r="E30">
-        <v>-25.65586325735966</v>
+        <v>-27.30265641567101</v>
       </c>
       <c r="F30">
-        <v>4.636199440799938</v>
+        <v>2.86714608725295</v>
       </c>
       <c r="G30">
-        <v>-6.297135484919787</v>
+        <v>-6.338831805986907</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.72000073044974</v>
       </c>
       <c r="E31">
-        <v>-26.06707586810017</v>
+        <v>-26.80842781942188</v>
       </c>
       <c r="F31">
-        <v>4.459841117468432</v>
+        <v>3.226441448288698</v>
       </c>
       <c r="G31">
-        <v>-5.94317857695199</v>
+        <v>-5.801517022781036</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.731020716191998</v>
       </c>
       <c r="E32">
-        <v>-26.15489203605692</v>
+        <v>-27.591939863755</v>
       </c>
       <c r="F32">
-        <v>4.164213901645181</v>
+        <v>3.003455655394824</v>
       </c>
       <c r="G32">
-        <v>-6.436936512497669</v>
+        <v>-5.532598098080499</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.794061583510564</v>
       </c>
       <c r="E33">
-        <v>-25.1861789902321</v>
+        <v>-27.02176422992323</v>
       </c>
       <c r="F33">
-        <v>4.183291223102565</v>
+        <v>2.728619330829462</v>
       </c>
       <c r="G33">
-        <v>-6.30088964356132</v>
+        <v>-6.367822253274305</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.895455548896974</v>
       </c>
       <c r="E34">
-        <v>-25.96048011843362</v>
+        <v>-27.71828881704301</v>
       </c>
       <c r="F34">
-        <v>4.352956805235424</v>
+        <v>2.974895102915788</v>
       </c>
       <c r="G34">
-        <v>-5.388804552582255</v>
+        <v>-6.15690077587626</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.026814033101372</v>
       </c>
       <c r="E35">
-        <v>-25.21966252704482</v>
+        <v>-26.42308185221318</v>
       </c>
       <c r="F35">
-        <v>3.890755401226252</v>
+        <v>2.704551752032529</v>
       </c>
       <c r="G35">
-        <v>-5.19899773463368</v>
+        <v>-5.685916083095226</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.185396887412391</v>
       </c>
       <c r="E36">
-        <v>-24.76886199652925</v>
+        <v>-27.52120057128118</v>
       </c>
       <c r="F36">
-        <v>3.964242523114473</v>
+        <v>2.847048859186024</v>
       </c>
       <c r="G36">
-        <v>-6.590509409518921</v>
+        <v>-5.993402863328273</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.367734426323879</v>
       </c>
       <c r="E37">
-        <v>-24.3304106146326</v>
+        <v>-25.53493941593284</v>
       </c>
       <c r="F37">
-        <v>4.130450875233928</v>
+        <v>2.740771106318629</v>
       </c>
       <c r="G37">
-        <v>-5.430007602364024</v>
+        <v>-7.051168510762968</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.563788552745547</v>
       </c>
       <c r="E38">
-        <v>-23.63460605488004</v>
+        <v>-26.31077116834895</v>
       </c>
       <c r="F38">
-        <v>3.645371255570318</v>
+        <v>2.81582451335722</v>
       </c>
       <c r="G38">
-        <v>-6.254654564559859</v>
+        <v>-6.317319881072724</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.772617899746941</v>
       </c>
       <c r="E39">
-        <v>-23.51492301533132</v>
+        <v>-24.95606005505833</v>
       </c>
       <c r="F39">
-        <v>4.195376482943283</v>
+        <v>2.672009762882079</v>
       </c>
       <c r="G39">
-        <v>-6.423167953599841</v>
+        <v>-6.182799173629978</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.997280944838608</v>
       </c>
       <c r="E40">
-        <v>-23.1133288833831</v>
+        <v>-25.71768598451238</v>
       </c>
       <c r="F40">
-        <v>3.555201375568857</v>
+        <v>2.754447990604364</v>
       </c>
       <c r="G40">
-        <v>-5.357718529968499</v>
+        <v>-7.180435382434889</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.236363507366498</v>
       </c>
       <c r="E41">
-        <v>-22.95911170105189</v>
+        <v>-25.44121358939609</v>
       </c>
       <c r="F41">
-        <v>3.95050229059212</v>
+        <v>3.151961342791496</v>
       </c>
       <c r="G41">
-        <v>-6.879278365272929</v>
+        <v>-6.986261954920017</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.485996563127313</v>
       </c>
       <c r="E42">
-        <v>-23.11960987683174</v>
+        <v>-23.68204182011039</v>
       </c>
       <c r="F42">
-        <v>3.513933166824336</v>
+        <v>3.421416234656194</v>
       </c>
       <c r="G42">
-        <v>-6.435416972095144</v>
+        <v>-7.845302174723339</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.749503211208833</v>
       </c>
       <c r="E43">
-        <v>-21.95472786546865</v>
+        <v>-21.37147852717674</v>
       </c>
       <c r="F43">
-        <v>3.565468541018651</v>
+        <v>2.778955839645789</v>
       </c>
       <c r="G43">
-        <v>-5.915326957330102</v>
+        <v>-6.751977957651333</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.032529235773563</v>
       </c>
       <c r="E44">
-        <v>-21.41079021003733</v>
+        <v>-21.9695767317398</v>
       </c>
       <c r="F44">
-        <v>3.620244177515955</v>
+        <v>2.947761469466565</v>
       </c>
       <c r="G44">
-        <v>-6.637062300892152</v>
+        <v>-7.559953012511399</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.330700664485029</v>
       </c>
       <c r="E45">
-        <v>-20.84613931449492</v>
+        <v>-23.04917852059044</v>
       </c>
       <c r="F45">
-        <v>3.888859705245471</v>
+        <v>2.668142353036576</v>
       </c>
       <c r="G45">
-        <v>-6.867118731507185</v>
+        <v>-7.998077230269626</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.640434671648858</v>
       </c>
       <c r="E46">
-        <v>-19.75049767070912</v>
+        <v>-21.50253256495872</v>
       </c>
       <c r="F46">
-        <v>3.887260162270877</v>
+        <v>2.527135513149509</v>
       </c>
       <c r="G46">
-        <v>-6.553219424564571</v>
+        <v>-7.473461699752399</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.962704750184107</v>
       </c>
       <c r="E47">
-        <v>-19.30390409254667</v>
+        <v>-20.69165948067126</v>
       </c>
       <c r="F47">
-        <v>4.003920691119893</v>
+        <v>2.652256198998803</v>
       </c>
       <c r="G47">
-        <v>-7.150051195475458</v>
+        <v>-8.087405680555781</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.297769334412036</v>
       </c>
       <c r="E48">
-        <v>-20.1652379627016</v>
+        <v>-19.88814969512027</v>
       </c>
       <c r="F48">
-        <v>4.254138307229749</v>
+        <v>2.808693085619996</v>
       </c>
       <c r="G48">
-        <v>-6.430265763236038</v>
+        <v>-7.831338293638693</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.633677174328387</v>
       </c>
       <c r="E49">
-        <v>-19.39496264789291</v>
+        <v>-20.35432892336589</v>
       </c>
       <c r="F49">
-        <v>3.990566882840908</v>
+        <v>2.896501660101536</v>
       </c>
       <c r="G49">
-        <v>-7.44961252968749</v>
+        <v>-8.715194362804393</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.967488950142627</v>
       </c>
       <c r="E50">
-        <v>-17.50493156520756</v>
+        <v>-20.11786106763336</v>
       </c>
       <c r="F50">
-        <v>4.084860733046172</v>
+        <v>3.222152772669688</v>
       </c>
       <c r="G50">
-        <v>-6.612594058811399</v>
+        <v>-7.689646944557887</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.298832402545713</v>
       </c>
       <c r="E51">
-        <v>-18.07191915333793</v>
+        <v>-19.86253664613289</v>
       </c>
       <c r="F51">
-        <v>4.071217106584662</v>
+        <v>2.837877618229714</v>
       </c>
       <c r="G51">
-        <v>-7.646642958002754</v>
+        <v>-8.714300515508791</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.624584951767035</v>
       </c>
       <c r="E52">
-        <v>-18.06466906645165</v>
+        <v>-18.5845922242203</v>
       </c>
       <c r="F52">
-        <v>3.857499160707939</v>
+        <v>3.352095843031494</v>
       </c>
       <c r="G52">
-        <v>-7.172407309502157</v>
+        <v>-8.100227423429377</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.932321899970423</v>
       </c>
       <c r="E53">
-        <v>-18.52607528309318</v>
+        <v>-18.6836616500861</v>
       </c>
       <c r="F53">
-        <v>3.66087573648247</v>
+        <v>3.472950025144594</v>
       </c>
       <c r="G53">
-        <v>-7.308454178438506</v>
+        <v>-8.474398522459964</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.22126047877737</v>
       </c>
       <c r="E54">
-        <v>-17.13044035019524</v>
+        <v>-17.93942506082151</v>
       </c>
       <c r="F54">
-        <v>3.829755800481271</v>
+        <v>3.345407852950594</v>
       </c>
       <c r="G54">
-        <v>-7.878510257027769</v>
+        <v>-8.695086109198861</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.49474238835307</v>
       </c>
       <c r="E55">
-        <v>-16.77699748237058</v>
+        <v>-16.7503202419914</v>
       </c>
       <c r="F55">
-        <v>3.691398500590734</v>
+        <v>3.026905588884735</v>
       </c>
       <c r="G55">
-        <v>-8.43244397884078</v>
+        <v>-8.99574985507547</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.74816376430493</v>
       </c>
       <c r="E56">
-        <v>-16.25077068878326</v>
+        <v>-16.45515430617144</v>
       </c>
       <c r="F56">
-        <v>3.963727818691955</v>
+        <v>2.743495080493184</v>
       </c>
       <c r="G56">
-        <v>-8.154675965913771</v>
+        <v>-9.717786458281594</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.97418538392923</v>
       </c>
       <c r="E57">
-        <v>-15.54418383241843</v>
+        <v>-17.52413682347409</v>
       </c>
       <c r="F57">
-        <v>3.958948194239159</v>
+        <v>3.078249334663282</v>
       </c>
       <c r="G57">
-        <v>-8.344750938051027</v>
+        <v>-8.991621604787998</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.1738535698254</v>
       </c>
       <c r="E58">
-        <v>-15.64830250680279</v>
+        <v>-17.40342582032563</v>
       </c>
       <c r="F58">
-        <v>3.660777546715713</v>
+        <v>2.680967203539804</v>
       </c>
       <c r="G58">
-        <v>-8.340291633209628</v>
+        <v>-10.04845698892616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.35349367069558</v>
       </c>
       <c r="E59">
-        <v>-15.18182892774668</v>
+        <v>-15.83396994111727</v>
       </c>
       <c r="F59">
-        <v>3.566985731285642</v>
+        <v>3.26874064958417</v>
       </c>
       <c r="G59">
-        <v>-7.960330390030856</v>
+        <v>-10.40679043809687</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.50733348990854</v>
       </c>
       <c r="E60">
-        <v>-15.52607899333577</v>
+        <v>-17.27305558211881</v>
       </c>
       <c r="F60">
-        <v>3.898366691855854</v>
+        <v>3.032701952535244</v>
       </c>
       <c r="G60">
-        <v>-8.365925187320205</v>
+        <v>-9.566007876942628</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.63349632362493</v>
       </c>
       <c r="E61">
-        <v>-15.13771706243796</v>
+        <v>-15.76841122290823</v>
       </c>
       <c r="F61">
-        <v>3.906487935790227</v>
+        <v>2.760076481427836</v>
       </c>
       <c r="G61">
-        <v>-8.359774193708239</v>
+        <v>-10.01537470735222</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.73813544299611</v>
       </c>
       <c r="E62">
-        <v>-15.45627256650753</v>
+        <v>-16.43206361720633</v>
       </c>
       <c r="F62">
-        <v>3.899125286989349</v>
+        <v>2.554698330901817</v>
       </c>
       <c r="G62">
-        <v>-8.65888529372693</v>
+        <v>-10.50446808423307</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.8289041090534</v>
       </c>
       <c r="E63">
-        <v>-15.25737745961664</v>
+        <v>-15.9897856747732</v>
       </c>
       <c r="F63">
-        <v>3.796037117835649</v>
+        <v>2.962919118783236</v>
       </c>
       <c r="G63">
-        <v>-8.200354873264635</v>
+        <v>-11.08788552461883</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.89880581988479</v>
       </c>
       <c r="E64">
-        <v>-14.0890990927478</v>
+        <v>-15.12873709848075</v>
       </c>
       <c r="F64">
-        <v>3.956417432186287</v>
+        <v>3.245140264032291</v>
       </c>
       <c r="G64">
-        <v>-9.547498616832563</v>
+        <v>-11.36722273613145</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.95079130205112</v>
       </c>
       <c r="E65">
-        <v>-14.59610251417257</v>
+        <v>-16.22483158966732</v>
       </c>
       <c r="F65">
-        <v>3.81695945668452</v>
+        <v>2.661915221377068</v>
       </c>
       <c r="G65">
-        <v>-8.792194341502302</v>
+        <v>-9.856763160020199</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.99343378149703</v>
       </c>
       <c r="E66">
-        <v>-14.1144223193987</v>
+        <v>-15.49072972523189</v>
       </c>
       <c r="F66">
-        <v>4.059150851214929</v>
+        <v>2.650415932725062</v>
       </c>
       <c r="G66">
-        <v>-9.07910608120878</v>
+        <v>-10.10326638087433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.03031747052112</v>
       </c>
       <c r="E67">
-        <v>-14.40053130720331</v>
+        <v>-15.26130364658129</v>
       </c>
       <c r="F67">
-        <v>3.906723907971628</v>
+        <v>3.230117229718433</v>
       </c>
       <c r="G67">
-        <v>-9.363303173573053</v>
+        <v>-10.40009651501646</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.05425012356222</v>
       </c>
       <c r="E68">
-        <v>-12.85530276393599</v>
+        <v>-16.57221083079571</v>
       </c>
       <c r="F68">
-        <v>3.566656320455231</v>
+        <v>3.060274272523045</v>
       </c>
       <c r="G68">
-        <v>-8.930796951594969</v>
+        <v>-10.70273003548894</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.0660293222395</v>
       </c>
       <c r="E69">
-        <v>-13.61336025587199</v>
+        <v>-14.34877084929564</v>
       </c>
       <c r="F69">
-        <v>3.749770733222001</v>
+        <v>2.373801106416662</v>
       </c>
       <c r="G69">
-        <v>-9.675749151023929</v>
+        <v>-10.35514923822978</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.07497760649558</v>
       </c>
       <c r="E70">
-        <v>-13.79704874704512</v>
+        <v>-15.65821986487959</v>
       </c>
       <c r="F70">
-        <v>3.533984467419715</v>
+        <v>3.147493708404041</v>
       </c>
       <c r="G70">
-        <v>-9.981779291219697</v>
+        <v>-9.606737518712281</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.07768308938389</v>
       </c>
       <c r="E71">
-        <v>-13.73919749159714</v>
+        <v>-16.07657840760421</v>
       </c>
       <c r="F71">
-        <v>3.329388667615924</v>
+        <v>2.221687736944618</v>
       </c>
       <c r="G71">
-        <v>-9.25529993589987</v>
+        <v>-10.0219064137012</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.06749261225623</v>
       </c>
       <c r="E72">
-        <v>-14.50605833700405</v>
+        <v>-14.99715322923987</v>
       </c>
       <c r="F72">
-        <v>3.659708545222791</v>
+        <v>2.582741011546503</v>
       </c>
       <c r="G72">
-        <v>-8.935709801175248</v>
+        <v>-10.0693498418245</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.04517414806159</v>
       </c>
       <c r="E73">
-        <v>-14.16654052675297</v>
+        <v>-14.81394022783754</v>
       </c>
       <c r="F73">
-        <v>3.136092609518793</v>
+        <v>2.067539305371235</v>
       </c>
       <c r="G73">
-        <v>-8.705666612742371</v>
+        <v>-8.609359532459433</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.01908141220628</v>
       </c>
       <c r="E74">
-        <v>-13.93064325874541</v>
+        <v>-14.30200076974442</v>
       </c>
       <c r="F74">
-        <v>3.055790801076435</v>
+        <v>2.208330761253802</v>
       </c>
       <c r="G74">
-        <v>-9.012173471495794</v>
+        <v>-9.357665314519675</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.98223261842005</v>
       </c>
       <c r="E75">
-        <v>-14.56891355623051</v>
+        <v>-14.7470229674262</v>
       </c>
       <c r="F75">
-        <v>3.435560312186984</v>
+        <v>2.018716819410068</v>
       </c>
       <c r="G75">
-        <v>-8.579418958602265</v>
+        <v>-10.35858889504508</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.93140105868619</v>
       </c>
       <c r="E76">
-        <v>-14.2931340176374</v>
+        <v>-14.02420153174388</v>
       </c>
       <c r="F76">
-        <v>2.909453207078</v>
+        <v>1.658403135470693</v>
       </c>
       <c r="G76">
-        <v>-8.347452343211073</v>
+        <v>-9.388883758955002</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.87229674387836</v>
       </c>
       <c r="E77">
-        <v>-15.31522418659062</v>
+        <v>-17.09931161986652</v>
       </c>
       <c r="F77">
-        <v>2.90651543260486</v>
+        <v>1.742797239998545</v>
       </c>
       <c r="G77">
-        <v>-8.54068888633833</v>
+        <v>-9.328062416307512</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.81185860735487</v>
       </c>
       <c r="E78">
-        <v>-14.86892043076467</v>
+        <v>-17.43094535687024</v>
       </c>
       <c r="F78">
-        <v>3.117816643254621</v>
+        <v>2.024478341530437</v>
       </c>
       <c r="G78">
-        <v>-7.757685276480989</v>
+        <v>-9.972536248074052</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.74196278281783</v>
       </c>
       <c r="E79">
-        <v>-16.27162884006259</v>
+        <v>-18.09263692192302</v>
       </c>
       <c r="F79">
-        <v>2.720116413769468</v>
+        <v>2.365152488412447</v>
       </c>
       <c r="G79">
-        <v>-7.926682005169704</v>
+        <v>-8.672223481704654</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.66405915370091</v>
       </c>
       <c r="E80">
-        <v>-15.7391074676046</v>
+        <v>-16.91702242716176</v>
       </c>
       <c r="F80">
-        <v>3.198903969831036</v>
+        <v>2.087212100252824</v>
       </c>
       <c r="G80">
-        <v>-8.171294904520913</v>
+        <v>-8.076262384270594</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.58669237399734</v>
       </c>
       <c r="E81">
-        <v>-16.27062351883288</v>
+        <v>-18.19769751890097</v>
       </c>
       <c r="F81">
-        <v>3.053125424020751</v>
+        <v>1.756494712461181</v>
       </c>
       <c r="G81">
-        <v>-7.814626659756453</v>
+        <v>-7.926274808068373</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.51235870193303</v>
       </c>
       <c r="E82">
-        <v>-19.44351694620315</v>
+        <v>-18.96412815927716</v>
       </c>
       <c r="F82">
-        <v>3.264349033080656</v>
+        <v>1.947594170453598</v>
       </c>
       <c r="G82">
-        <v>-7.007518967827677</v>
+        <v>-8.234443560682511</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.43428372997165</v>
       </c>
       <c r="E83">
-        <v>-18.52890105087397</v>
+        <v>-17.77534033362758</v>
       </c>
       <c r="F83">
-        <v>2.80899715715576</v>
+        <v>2.050314919834916</v>
       </c>
       <c r="G83">
-        <v>-7.479529929725884</v>
+        <v>-8.595696911018861</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.3515071488124</v>
       </c>
       <c r="E84">
-        <v>-20.0563689190832</v>
+        <v>-20.28574971299373</v>
       </c>
       <c r="F84">
-        <v>2.76252647447902</v>
+        <v>1.304880382496722</v>
       </c>
       <c r="G84">
-        <v>-6.44502086470457</v>
+        <v>-7.183424805056851</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.27313822433426</v>
       </c>
       <c r="E85">
-        <v>-21.42981885781756</v>
+        <v>-22.01205834640576</v>
       </c>
       <c r="F85">
-        <v>2.914438713299803</v>
+        <v>2.383901982745335</v>
       </c>
       <c r="G85">
-        <v>-7.107699386391562</v>
+        <v>-7.395792990855559</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.19433315690276</v>
       </c>
       <c r="E86">
-        <v>-22.48426044508158</v>
+        <v>-23.08615351086307</v>
       </c>
       <c r="F86">
-        <v>2.707074595555824</v>
+        <v>1.987277089576764</v>
       </c>
       <c r="G86">
-        <v>-6.98433521741616</v>
+        <v>-6.488696892004175</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.1076012808551</v>
       </c>
       <c r="E87">
-        <v>-22.74139625618512</v>
+        <v>-23.67895792931116</v>
       </c>
       <c r="F87">
-        <v>2.688610168287715</v>
+        <v>2.264899152847383</v>
       </c>
       <c r="G87">
-        <v>-6.361207783286841</v>
+        <v>-7.43153695104307</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.01082605478592</v>
       </c>
       <c r="E88">
-        <v>-24.63085222267149</v>
+        <v>-24.72388972115908</v>
       </c>
       <c r="F88">
-        <v>2.669433073357659</v>
+        <v>1.825430263548429</v>
       </c>
       <c r="G88">
-        <v>-6.21095205289594</v>
+        <v>-6.790810656826984</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.90763651024637</v>
       </c>
       <c r="E89">
-        <v>-26.38186821026937</v>
+        <v>-26.21522942373512</v>
       </c>
       <c r="F89">
-        <v>2.631460556623167</v>
+        <v>1.839065971480363</v>
       </c>
       <c r="G89">
-        <v>-5.828289404557123</v>
+        <v>-6.934114241585417</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.78687980033594</v>
       </c>
       <c r="E90">
-        <v>-28.13144867160682</v>
+        <v>-26.50050970079633</v>
       </c>
       <c r="F90">
-        <v>2.265155713205685</v>
+        <v>1.827786817950603</v>
       </c>
       <c r="G90">
-        <v>-6.526397384605395</v>
+        <v>-7.379256815886899</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.63930768557369</v>
       </c>
       <c r="E91">
-        <v>-29.50603525731711</v>
+        <v>-30.70393890114412</v>
       </c>
       <c r="F91">
-        <v>2.391494268903951</v>
+        <v>1.805033715063485</v>
       </c>
       <c r="G91">
-        <v>-6.409313320517991</v>
+        <v>-6.667145228207509</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.46261373681064</v>
       </c>
       <c r="E92">
-        <v>-30.90972408123768</v>
+        <v>-31.30532251359975</v>
       </c>
       <c r="F92">
-        <v>2.607576687712425</v>
+        <v>1.829953327642925</v>
       </c>
       <c r="G92">
-        <v>-6.561376608773334</v>
+        <v>-7.590691427843532</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.25545015424178</v>
       </c>
       <c r="E93">
-        <v>-34.01996380647483</v>
+        <v>-34.06143104296306</v>
       </c>
       <c r="F93">
-        <v>2.339317493813883</v>
+        <v>1.692479735653203</v>
       </c>
       <c r="G93">
-        <v>-6.650337588504629</v>
+        <v>-6.185484026062326</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.00603147307332</v>
       </c>
       <c r="E94">
-        <v>-35.60578332650989</v>
+        <v>-34.18007932620103</v>
       </c>
       <c r="F94">
-        <v>2.397792667329654</v>
+        <v>1.296462985556161</v>
       </c>
       <c r="G94">
-        <v>-6.270263786777522</v>
+        <v>-6.834708490677721</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.709828135748147</v>
       </c>
       <c r="E95">
-        <v>-37.06135714137336</v>
+        <v>-37.04968047114458</v>
       </c>
       <c r="F95">
-        <v>2.386405821797644</v>
+        <v>1.120164843049442</v>
       </c>
       <c r="G95">
-        <v>-5.393826650165329</v>
+        <v>-6.730360095279893</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.36913593010221</v>
       </c>
       <c r="E96">
-        <v>-40.19913904552515</v>
+        <v>-39.58491494502077</v>
       </c>
       <c r="F96">
-        <v>2.21259251387225</v>
+        <v>1.07298307641667</v>
       </c>
       <c r="G96">
-        <v>-6.020297735289312</v>
+        <v>-6.919898759039786</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.989806951380945</v>
       </c>
       <c r="E97">
-        <v>-41.31138660349708</v>
+        <v>-41.47783745836002</v>
       </c>
       <c r="F97">
-        <v>1.905355149982912</v>
+        <v>1.255997715710768</v>
       </c>
       <c r="G97">
-        <v>-6.422562123766154</v>
+        <v>-6.916906025872285</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.564044801976058</v>
       </c>
       <c r="E98">
-        <v>-43.97292248168421</v>
+        <v>-43.47986449596606</v>
       </c>
       <c r="F98">
-        <v>2.055837302362053</v>
+        <v>0.7839345749661548</v>
       </c>
       <c r="G98">
-        <v>-7.286988601161871</v>
+        <v>-6.859117142938767</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.106832894772946</v>
       </c>
       <c r="E99">
-        <v>-47.3494545924684</v>
+        <v>-45.14992268949182</v>
       </c>
       <c r="F99">
-        <v>1.889700217008793</v>
+        <v>0.7466272147161478</v>
       </c>
       <c r="G99">
-        <v>-6.068631700162672</v>
+        <v>-6.983477786121489</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.618594657012129</v>
       </c>
       <c r="E100">
-        <v>-49.03073660882217</v>
+        <v>-47.98665390585069</v>
       </c>
       <c r="F100">
-        <v>1.98773319688041</v>
+        <v>1.008176246650972</v>
       </c>
       <c r="G100">
-        <v>-6.79805413046691</v>
+        <v>-8.336348773472356</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.134754405928137</v>
       </c>
       <c r="E101">
-        <v>-50.06917456894308</v>
+        <v>-50.05318452722199</v>
       </c>
       <c r="F101">
-        <v>1.344827780507767</v>
+        <v>1.047186090760077</v>
       </c>
       <c r="G101">
-        <v>-7.041766561431437</v>
+        <v>-7.244395122253609</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.615911813949253</v>
       </c>
       <c r="E102">
-        <v>-53.07293062424536</v>
+        <v>-52.54639929078102</v>
       </c>
       <c r="F102">
-        <v>1.584274612686718</v>
+        <v>0.2703173665592836</v>
       </c>
       <c r="G102">
-        <v>-6.960327141165366</v>
+        <v>-7.831871291470517</v>
       </c>
     </row>
   </sheetData>
